--- a/ma_tram.xlsx
+++ b/ma_tram.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Desktop\New folder\kpi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PYTHON\kpi_Streamlit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FF01E890-27DD-49CC-9615-D8DFD48D9751}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C236EE-DD49-4FD8-91F2-CA9F181EEF62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="97" uniqueCount="95">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="99">
   <si>
     <t>STT</t>
   </si>
@@ -310,13 +310,25 @@
   </si>
   <si>
     <t>Cc Nội Hoá</t>
+  </si>
+  <si>
+    <t>HCM</t>
+  </si>
+  <si>
+    <t>VTU</t>
+  </si>
+  <si>
+    <t>BDG</t>
+  </si>
+  <si>
+    <t>Khu vực</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -326,27 +338,12 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFC00000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF0070C0"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -355,13 +352,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
+        <fgColor theme="4" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -430,34 +433,51 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -738,539 +758,599 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="B2:D49"/>
+  <dimension ref="B2:E49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="4" max="4" width="45.5703125" customWidth="1"/>
+    <col min="5" max="5" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
+    <row r="2" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B2" s="17" t="s">
         <v>0</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="17" t="s">
         <v>2</v>
       </c>
-    </row>
-    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="17" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="3" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B3" s="1">
         <v>1</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D3" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E3" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" s="1">
         <v>2</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E4" s="2"/>
+    </row>
+    <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
         <v>3</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>7</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
         <v>4</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="1" t="s">
         <v>9</v>
       </c>
       <c r="D6" s="1" t="s">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
         <v>5</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D7" s="1" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="8" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
         <v>6</v>
       </c>
       <c r="C8" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="3" t="s">
         <v>14</v>
       </c>
-    </row>
-    <row r="9" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E8" s="2"/>
+    </row>
+    <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
         <v>7</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="10" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E9" s="2"/>
+    </row>
+    <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
         <v>8</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="11" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B11" s="5">
+      <c r="E10" s="2"/>
+    </row>
+    <row r="11" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B11" s="4">
         <v>9</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D11" s="1" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="12" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B12" s="6">
+      <c r="E11" s="2"/>
+    </row>
+    <row r="12" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B12" s="5">
         <v>10</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D12" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="13" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B13" s="7"/>
-      <c r="C13" s="2" t="s">
+      <c r="E12" s="2"/>
+    </row>
+    <row r="13" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B13" s="6"/>
+      <c r="C13" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="14" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B14" s="8"/>
-      <c r="C14" s="2" t="s">
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B14" s="7"/>
+      <c r="C14" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="15" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E14" s="2"/>
+    </row>
+    <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
         <v>11</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>25</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="16" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E15" s="2"/>
+    </row>
+    <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
         <v>12</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D16" s="1" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="17" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E16" s="2"/>
+    </row>
+    <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
         <v>13</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>29</v>
       </c>
       <c r="D17" s="1" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="18" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E17" s="2"/>
+    </row>
+    <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
         <v>14</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>31</v>
       </c>
       <c r="D18" s="1" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="19" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E18" s="2"/>
+    </row>
+    <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
         <v>15</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>33</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="20" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E19" s="2"/>
+    </row>
+    <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
         <v>16</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="21" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E20" s="2"/>
+    </row>
+    <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
         <v>17</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D21" s="1" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="22" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E21" s="2"/>
+    </row>
+    <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
         <v>18</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D22" s="1" t="s">
         <v>40</v>
       </c>
-    </row>
-    <row r="23" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E22" s="2"/>
+    </row>
+    <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
         <v>19</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D23" s="1" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="24" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E23" s="2"/>
+    </row>
+    <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="1">
         <v>20</v>
       </c>
-      <c r="C24" s="2" t="s">
+      <c r="C24" s="1" t="s">
         <v>43</v>
       </c>
       <c r="D24" s="1" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="25" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B25" s="9">
+      <c r="E24" s="2"/>
+    </row>
+    <row r="25" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B25" s="8">
         <v>21</v>
       </c>
-      <c r="C25" s="2" t="s">
+      <c r="C25" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="3" t="s">
         <v>46</v>
       </c>
-    </row>
-    <row r="26" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B26" s="9">
+      <c r="E25" s="2"/>
+    </row>
+    <row r="26" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B26" s="8">
         <v>22</v>
       </c>
-      <c r="C26" s="2" t="s">
+      <c r="C26" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D26" s="1" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="27" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B27" s="9">
+      <c r="E26" s="2"/>
+    </row>
+    <row r="27" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B27" s="8">
         <v>23</v>
       </c>
-      <c r="C27" s="2" t="s">
+      <c r="C27" s="1" t="s">
         <v>49</v>
       </c>
       <c r="D27" s="1" t="s">
         <v>50</v>
       </c>
-    </row>
-    <row r="28" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E27" s="2"/>
+    </row>
+    <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="1">
         <v>24</v>
       </c>
-      <c r="C28" s="2" t="s">
+      <c r="C28" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D28" s="1" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="29" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E28" s="2"/>
+    </row>
+    <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" s="1">
         <v>25</v>
       </c>
-      <c r="C29" s="2" t="s">
+      <c r="C29" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="30" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E29" s="2"/>
+    </row>
+    <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30" s="1">
         <v>26</v>
       </c>
-      <c r="C30" s="2" t="s">
+      <c r="C30" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="31" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E30" s="2"/>
+    </row>
+    <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" s="1">
         <v>27</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="1" t="s">
         <v>57</v>
       </c>
       <c r="D31" s="1" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="32" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E31" s="2"/>
+    </row>
+    <row r="32" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B32" s="1">
         <v>28</v>
       </c>
-      <c r="C32" s="2" t="s">
+      <c r="C32" s="1" t="s">
         <v>59</v>
       </c>
       <c r="D32" s="1" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="33" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E32" s="2"/>
+    </row>
+    <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" s="1">
         <v>29</v>
       </c>
-      <c r="C33" s="2" t="s">
+      <c r="C33" s="1" t="s">
         <v>61</v>
       </c>
       <c r="D33" s="1" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="34" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B34" s="4">
+      <c r="E33" s="2"/>
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B34" s="3">
         <v>30</v>
       </c>
-      <c r="C34" s="2" t="s">
+      <c r="C34" s="1" t="s">
         <v>63</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="35" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E34" s="2"/>
+    </row>
+    <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="1">
         <v>31</v>
       </c>
-      <c r="C35" s="2" t="s">
+      <c r="C35" s="1" t="s">
         <v>65</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="3" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="36" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B36" s="10">
+      <c r="E35" s="2"/>
+    </row>
+    <row r="36" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B36" s="9">
         <v>32</v>
       </c>
-      <c r="C36" s="11" t="s">
+      <c r="C36" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="D36" s="12" t="s">
+      <c r="D36" s="9" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="37" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B37" s="10">
+      <c r="E36" s="10" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="37" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B37" s="9">
         <v>33</v>
       </c>
-      <c r="C37" s="11" t="s">
+      <c r="C37" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D37" s="12" t="s">
+      <c r="D37" s="9" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="38" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B38" s="10">
+      <c r="E37" s="11"/>
+    </row>
+    <row r="38" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B38" s="9">
         <v>34</v>
       </c>
-      <c r="C38" s="11" t="s">
+      <c r="C38" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="D38" s="12" t="s">
+      <c r="D38" s="9" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="39" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B39" s="10">
+      <c r="E38" s="11"/>
+    </row>
+    <row r="39" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B39" s="9">
         <v>35</v>
       </c>
-      <c r="C39" s="11" t="s">
+      <c r="C39" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="D39" s="12" t="s">
+      <c r="D39" s="9" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="40" spans="2:4" x14ac:dyDescent="0.25">
-      <c r="B40" s="10">
+      <c r="E39" s="11"/>
+    </row>
+    <row r="40" spans="2:5" x14ac:dyDescent="0.25">
+      <c r="B40" s="9">
         <v>36</v>
       </c>
-      <c r="C40" s="11" t="s">
+      <c r="C40" s="9" t="s">
         <v>75</v>
       </c>
-      <c r="D40" s="12" t="s">
+      <c r="D40" s="9" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="41" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E40" s="12"/>
+    </row>
+    <row r="41" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B41" s="13">
         <v>37</v>
       </c>
-      <c r="C41" s="14" t="s">
+      <c r="C41" s="13" t="s">
         <v>77</v>
       </c>
-      <c r="D41" s="15" t="s">
+      <c r="D41" s="13" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="42" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E41" s="14" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="42" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B42" s="13">
         <v>38</v>
       </c>
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="13" t="s">
         <v>79</v>
       </c>
-      <c r="D42" s="15" t="s">
+      <c r="D42" s="13" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="43" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E42" s="15"/>
+    </row>
+    <row r="43" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B43" s="13">
         <v>39</v>
       </c>
-      <c r="C43" s="14" t="s">
+      <c r="C43" s="13" t="s">
         <v>81</v>
       </c>
-      <c r="D43" s="15" t="s">
+      <c r="D43" s="13" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="44" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E43" s="15"/>
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B44" s="13">
         <v>40</v>
       </c>
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="13" t="s">
         <v>83</v>
       </c>
-      <c r="D44" s="15" t="s">
+      <c r="D44" s="13" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="45" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E44" s="15"/>
+    </row>
+    <row r="45" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B45" s="13">
         <v>41</v>
       </c>
-      <c r="C45" s="16" t="s">
+      <c r="C45" s="13" t="s">
         <v>85</v>
       </c>
-      <c r="D45" s="15" t="s">
+      <c r="D45" s="13" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="46" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E45" s="15"/>
+    </row>
+    <row r="46" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B46" s="13">
         <v>42</v>
       </c>
-      <c r="C46" s="16" t="s">
+      <c r="C46" s="13" t="s">
         <v>87</v>
       </c>
-      <c r="D46" s="15" t="s">
+      <c r="D46" s="13" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="47" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E46" s="15"/>
+    </row>
+    <row r="47" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B47" s="13">
         <v>43</v>
       </c>
-      <c r="C47" s="16" t="s">
+      <c r="C47" s="13" t="s">
         <v>89</v>
       </c>
-      <c r="D47" s="15" t="s">
+      <c r="D47" s="13" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="48" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E47" s="15"/>
+    </row>
+    <row r="48" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B48" s="13">
         <v>44</v>
       </c>
-      <c r="C48" s="16" t="s">
+      <c r="C48" s="13" t="s">
         <v>91</v>
       </c>
-      <c r="D48" s="15" t="s">
+      <c r="D48" s="13" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="49" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="E48" s="15"/>
+    </row>
+    <row r="49" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B49" s="13">
         <v>45</v>
       </c>
-      <c r="C49" s="16" t="s">
+      <c r="C49" s="13" t="s">
         <v>93</v>
       </c>
-      <c r="D49" s="15" t="s">
+      <c r="D49" s="13" t="s">
         <v>94</v>
       </c>
+      <c r="E49" s="16"/>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="4">
     <mergeCell ref="B12:B14"/>
+    <mergeCell ref="E3:E35"/>
+    <mergeCell ref="E36:E40"/>
+    <mergeCell ref="E41:E49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ma_tram.xlsx
+++ b/ma_tram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PYTHON\kpi_Streamlit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{12C236EE-DD49-4FD8-91F2-CA9F181EEF62}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB9DD8E-3CF5-45B4-AE81-BFF7F34C3D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="99">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="99">
   <si>
     <t>STT</t>
   </si>
@@ -433,7 +433,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -446,37 +446,25 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -766,16 +754,16 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B2" s="17" t="s">
+      <c r="B2" s="10" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="17" t="s">
+      <c r="C2" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="17" t="s">
+      <c r="D2" s="10" t="s">
         <v>2</v>
       </c>
-      <c r="E2" s="17" t="s">
+      <c r="E2" s="10" t="s">
         <v>98</v>
       </c>
     </row>
@@ -803,7 +791,9 @@
       <c r="D4" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="E4" s="2"/>
+      <c r="E4" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="5" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B5" s="1">
@@ -815,7 +805,9 @@
       <c r="D5" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="E5" s="2"/>
+      <c r="E5" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B6" s="1">
@@ -827,7 +819,9 @@
       <c r="D6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E6" s="2"/>
+      <c r="E6" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" s="1">
@@ -839,7 +833,9 @@
       <c r="D7" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="2"/>
+      <c r="E7" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" s="1">
@@ -851,7 +847,9 @@
       <c r="D8" s="3" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="2"/>
+      <c r="E8" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" s="1">
@@ -863,7 +861,9 @@
       <c r="D9" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E9" s="2"/>
+      <c r="E9" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" s="1">
@@ -875,7 +875,9 @@
       <c r="D10" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="E10" s="2"/>
+      <c r="E10" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" s="4">
@@ -887,10 +889,12 @@
       <c r="D11" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="E11" s="2"/>
+      <c r="E11" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B12" s="5">
+      <c r="B12" s="11">
         <v>10</v>
       </c>
       <c r="C12" s="1" t="s">
@@ -899,27 +903,33 @@
       <c r="D12" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="2"/>
+      <c r="E12" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B13" s="6"/>
+      <c r="B13" s="12"/>
       <c r="C13" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D13" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E13" s="2"/>
+      <c r="E13" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B14" s="7"/>
+      <c r="B14" s="13"/>
       <c r="C14" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="E14" s="2"/>
+      <c r="E14" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" s="1">
@@ -931,7 +941,9 @@
       <c r="D15" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="2"/>
+      <c r="E15" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" s="1">
@@ -943,7 +955,9 @@
       <c r="D16" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="E16" s="2"/>
+      <c r="E16" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="17" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B17" s="1">
@@ -955,7 +969,9 @@
       <c r="D17" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="2"/>
+      <c r="E17" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="18" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B18" s="1">
@@ -967,7 +983,9 @@
       <c r="D18" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="E18" s="2"/>
+      <c r="E18" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="19" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B19" s="1">
@@ -979,7 +997,9 @@
       <c r="D19" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="E19" s="2"/>
+      <c r="E19" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="20" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B20" s="1">
@@ -991,7 +1011,9 @@
       <c r="D20" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="E20" s="2"/>
+      <c r="E20" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="21" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B21" s="1">
@@ -1003,7 +1025,9 @@
       <c r="D21" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="E21" s="2"/>
+      <c r="E21" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="22" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B22" s="1">
@@ -1015,7 +1039,9 @@
       <c r="D22" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E22" s="2"/>
+      <c r="E22" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="23" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B23" s="1">
@@ -1027,7 +1053,9 @@
       <c r="D23" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="E23" s="2"/>
+      <c r="E23" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="24" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B24" s="1">
@@ -1039,10 +1067,12 @@
       <c r="D24" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="E24" s="2"/>
+      <c r="E24" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="25" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B25" s="8">
+      <c r="B25" s="5">
         <v>21</v>
       </c>
       <c r="C25" s="1" t="s">
@@ -1051,10 +1081,12 @@
       <c r="D25" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="E25" s="2"/>
+      <c r="E25" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="26" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B26" s="8">
+      <c r="B26" s="5">
         <v>22</v>
       </c>
       <c r="C26" s="1" t="s">
@@ -1063,10 +1095,12 @@
       <c r="D26" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E26" s="2"/>
+      <c r="E26" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="27" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B27" s="8">
+      <c r="B27" s="5">
         <v>23</v>
       </c>
       <c r="C27" s="1" t="s">
@@ -1075,7 +1109,9 @@
       <c r="D27" s="1" t="s">
         <v>50</v>
       </c>
-      <c r="E27" s="2"/>
+      <c r="E27" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="28" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B28" s="1">
@@ -1087,7 +1123,9 @@
       <c r="D28" s="1" t="s">
         <v>52</v>
       </c>
-      <c r="E28" s="2"/>
+      <c r="E28" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="29" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B29" s="1">
@@ -1099,7 +1137,9 @@
       <c r="D29" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="E29" s="2"/>
+      <c r="E29" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="30" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B30" s="1">
@@ -1111,7 +1151,9 @@
       <c r="D30" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="E30" s="2"/>
+      <c r="E30" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="31" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B31" s="1">
@@ -1123,7 +1165,9 @@
       <c r="D31" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="E31" s="2"/>
+      <c r="E31" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="32" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B32" s="1">
@@ -1135,7 +1179,9 @@
       <c r="D32" s="1" t="s">
         <v>60</v>
       </c>
-      <c r="E32" s="2"/>
+      <c r="E32" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="33" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B33" s="1">
@@ -1147,7 +1193,9 @@
       <c r="D33" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E33" s="2"/>
+      <c r="E33" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="34" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B34" s="3">
@@ -1159,7 +1207,9 @@
       <c r="D34" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="E34" s="2"/>
+      <c r="E34" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="35" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B35" s="1">
@@ -1171,186 +1221,209 @@
       <c r="D35" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E35" s="2"/>
+      <c r="E35" s="2" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="36" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B36" s="9">
+      <c r="B36" s="6">
         <v>32</v>
       </c>
-      <c r="C36" s="9" t="s">
+      <c r="C36" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="D36" s="9" t="s">
+      <c r="D36" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="E36" s="10" t="s">
+      <c r="E36" s="7" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="37" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B37" s="9">
+      <c r="B37" s="6">
         <v>33</v>
       </c>
-      <c r="C37" s="9" t="s">
+      <c r="C37" s="6" t="s">
         <v>69</v>
       </c>
-      <c r="D37" s="9" t="s">
+      <c r="D37" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="E37" s="11"/>
+      <c r="E37" s="7" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="38" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B38" s="9">
+      <c r="B38" s="6">
         <v>34</v>
       </c>
-      <c r="C38" s="9" t="s">
+      <c r="C38" s="6" t="s">
         <v>71</v>
       </c>
-      <c r="D38" s="9" t="s">
+      <c r="D38" s="6" t="s">
         <v>72</v>
       </c>
-      <c r="E38" s="11"/>
+      <c r="E38" s="7" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="39" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B39" s="9">
+      <c r="B39" s="6">
         <v>35</v>
       </c>
-      <c r="C39" s="9" t="s">
+      <c r="C39" s="6" t="s">
         <v>73</v>
       </c>
-      <c r="D39" s="9" t="s">
+      <c r="D39" s="6" t="s">
         <v>74</v>
       </c>
-      <c r="E39" s="11"/>
+      <c r="E39" s="7" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="40" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B40" s="9">
+      <c r="B40" s="6">
         <v>36</v>
       </c>
-      <c r="C40" s="9" t="s">
+      <c r="C40" s="6" t="s">
         <v>75</v>
       </c>
-      <c r="D40" s="9" t="s">
+      <c r="D40" s="6" t="s">
         <v>76</v>
       </c>
-      <c r="E40" s="12"/>
+      <c r="E40" s="7" t="s">
+        <v>96</v>
+      </c>
     </row>
     <row r="41" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B41" s="13">
+      <c r="B41" s="8">
         <v>37</v>
       </c>
-      <c r="C41" s="13" t="s">
+      <c r="C41" s="8" t="s">
         <v>77</v>
       </c>
-      <c r="D41" s="13" t="s">
+      <c r="D41" s="8" t="s">
         <v>78</v>
       </c>
-      <c r="E41" s="14" t="s">
+      <c r="E41" s="9" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="42" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B42" s="13">
+      <c r="B42" s="8">
         <v>38</v>
       </c>
-      <c r="C42" s="13" t="s">
+      <c r="C42" s="8" t="s">
         <v>79</v>
       </c>
-      <c r="D42" s="13" t="s">
+      <c r="D42" s="8" t="s">
         <v>80</v>
       </c>
-      <c r="E42" s="15"/>
+      <c r="E42" s="9" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="43" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B43" s="13">
+      <c r="B43" s="8">
         <v>39</v>
       </c>
-      <c r="C43" s="13" t="s">
+      <c r="C43" s="8" t="s">
         <v>81</v>
       </c>
-      <c r="D43" s="13" t="s">
+      <c r="D43" s="8" t="s">
         <v>82</v>
       </c>
-      <c r="E43" s="15"/>
+      <c r="E43" s="9" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="44" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B44" s="13">
+      <c r="B44" s="8">
         <v>40</v>
       </c>
-      <c r="C44" s="13" t="s">
+      <c r="C44" s="8" t="s">
         <v>83</v>
       </c>
-      <c r="D44" s="13" t="s">
+      <c r="D44" s="8" t="s">
         <v>84</v>
       </c>
-      <c r="E44" s="15"/>
+      <c r="E44" s="9" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="45" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B45" s="13">
+      <c r="B45" s="8">
         <v>41</v>
       </c>
-      <c r="C45" s="13" t="s">
+      <c r="C45" s="8" t="s">
         <v>85</v>
       </c>
-      <c r="D45" s="13" t="s">
+      <c r="D45" s="8" t="s">
         <v>86</v>
       </c>
-      <c r="E45" s="15"/>
+      <c r="E45" s="9" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="46" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B46" s="13">
+      <c r="B46" s="8">
         <v>42</v>
       </c>
-      <c r="C46" s="13" t="s">
+      <c r="C46" s="8" t="s">
         <v>87</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="D46" s="8" t="s">
         <v>88</v>
       </c>
-      <c r="E46" s="15"/>
+      <c r="E46" s="9" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="47" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B47" s="13">
+      <c r="B47" s="8">
         <v>43</v>
       </c>
-      <c r="C47" s="13" t="s">
+      <c r="C47" s="8" t="s">
         <v>89</v>
       </c>
-      <c r="D47" s="13" t="s">
+      <c r="D47" s="8" t="s">
         <v>90</v>
       </c>
-      <c r="E47" s="15"/>
+      <c r="E47" s="9" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="48" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B48" s="13">
+      <c r="B48" s="8">
         <v>44</v>
       </c>
-      <c r="C48" s="13" t="s">
+      <c r="C48" s="8" t="s">
         <v>91</v>
       </c>
-      <c r="D48" s="13" t="s">
+      <c r="D48" s="8" t="s">
         <v>92</v>
       </c>
-      <c r="E48" s="15"/>
+      <c r="E48" s="9" t="s">
+        <v>97</v>
+      </c>
     </row>
     <row r="49" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B49" s="13">
+      <c r="B49" s="8">
         <v>45</v>
       </c>
-      <c r="C49" s="13" t="s">
+      <c r="C49" s="8" t="s">
         <v>93</v>
       </c>
-      <c r="D49" s="13" t="s">
+      <c r="D49" s="8" t="s">
         <v>94</v>
       </c>
-      <c r="E49" s="16"/>
+      <c r="E49" s="9" t="s">
+        <v>97</v>
+      </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="1">
     <mergeCell ref="B12:B14"/>
-    <mergeCell ref="E3:E35"/>
-    <mergeCell ref="E36:E40"/>
-    <mergeCell ref="E41:E49"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/ma_tram.xlsx
+++ b/ma_tram.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\PYTHON\kpi_Streamlit\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DFB9DD8E-3CF5-45B4-AE81-BFF7F34C3D64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C06768C5-8BAC-4E65-A7DE-7753C154B1D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -749,7 +749,7 @@
   <dimension ref="B2:E49"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="4" max="4" width="45.5703125" customWidth="1"/>
+    <col min="4" max="4" width="28.140625" customWidth="1"/>
     <col min="5" max="5" width="15.28515625" customWidth="1"/>
   </cols>
   <sheetData>
